--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856882</v>
       </c>
       <c r="B2" t="n">
-        <v>91968</v>
+        <v>91978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133856884</v>
       </c>
       <c r="B3" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>133856880</v>
       </c>
       <c r="B4" t="n">
-        <v>98039</v>
+        <v>98049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>133856878</v>
       </c>
       <c r="B5" t="n">
-        <v>80482</v>
+        <v>80478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133856881</v>
+        <v>133856885</v>
       </c>
       <c r="B6" t="n">
-        <v>93236</v>
+        <v>79115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768793</v>
+        <v>768955</v>
       </c>
       <c r="R6" t="n">
-        <v>7288168</v>
+        <v>7287877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133856885</v>
+        <v>133856881</v>
       </c>
       <c r="B7" t="n">
-        <v>79105</v>
+        <v>93246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768955</v>
+        <v>768793</v>
       </c>
       <c r="R7" t="n">
-        <v>7287877</v>
+        <v>7288168</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
         <v>133856879</v>
       </c>
       <c r="B8" t="n">
-        <v>93244</v>
+        <v>93254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>133856883</v>
       </c>
       <c r="B9" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133856885</v>
+        <v>133856881</v>
       </c>
       <c r="B6" t="n">
-        <v>79115</v>
+        <v>93246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768955</v>
+        <v>768793</v>
       </c>
       <c r="R6" t="n">
-        <v>7287877</v>
+        <v>7288168</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133856881</v>
+        <v>133856885</v>
       </c>
       <c r="B7" t="n">
-        <v>93246</v>
+        <v>79115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768793</v>
+        <v>768955</v>
       </c>
       <c r="R7" t="n">
-        <v>7288168</v>
+        <v>7287877</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133856881</v>
+        <v>133856885</v>
       </c>
       <c r="B6" t="n">
-        <v>93246</v>
+        <v>79115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768793</v>
+        <v>768955</v>
       </c>
       <c r="R6" t="n">
-        <v>7288168</v>
+        <v>7287877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133856885</v>
+        <v>133856881</v>
       </c>
       <c r="B7" t="n">
-        <v>79115</v>
+        <v>93246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768955</v>
+        <v>768793</v>
       </c>
       <c r="R7" t="n">
-        <v>7287877</v>
+        <v>7288168</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856882</v>
       </c>
       <c r="B2" t="n">
-        <v>91978</v>
+        <v>91980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133856884</v>
       </c>
       <c r="B3" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>133856880</v>
       </c>
       <c r="B4" t="n">
-        <v>98049</v>
+        <v>98051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>133856878</v>
       </c>
       <c r="B5" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133856885</v>
+        <v>133856881</v>
       </c>
       <c r="B6" t="n">
-        <v>79115</v>
+        <v>93248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768955</v>
+        <v>768793</v>
       </c>
       <c r="R6" t="n">
-        <v>7287877</v>
+        <v>7288168</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133856881</v>
+        <v>133856885</v>
       </c>
       <c r="B7" t="n">
-        <v>93246</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768793</v>
+        <v>768955</v>
       </c>
       <c r="R7" t="n">
-        <v>7288168</v>
+        <v>7287877</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
         <v>133856879</v>
       </c>
       <c r="B8" t="n">
-        <v>93254</v>
+        <v>93256</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>133856883</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133856879</v>
+        <v>133856883</v>
       </c>
       <c r="B8" t="n">
-        <v>93256</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768664</v>
+        <v>768858</v>
       </c>
       <c r="R8" t="n">
-        <v>7288089</v>
+        <v>7288036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,32 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133856883</v>
+        <v>133856879</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>93256</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768858</v>
+        <v>768664</v>
       </c>
       <c r="R9" t="n">
-        <v>7288036</v>
+        <v>7288089</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133856881</v>
+        <v>133856885</v>
       </c>
       <c r="B6" t="n">
-        <v>93249</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768793</v>
+        <v>768955</v>
       </c>
       <c r="R6" t="n">
-        <v>7288168</v>
+        <v>7287877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133856885</v>
+        <v>133856881</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>93249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768955</v>
+        <v>768793</v>
       </c>
       <c r="R7" t="n">
-        <v>7287877</v>
+        <v>7288168</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856882</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133856884</v>
       </c>
       <c r="B3" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>133856880</v>
       </c>
       <c r="B4" t="n">
-        <v>98052</v>
+        <v>98059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>133856878</v>
       </c>
       <c r="B5" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133856885</v>
+        <v>133856881</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>93256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768955</v>
+        <v>768793</v>
       </c>
       <c r="R6" t="n">
-        <v>7287877</v>
+        <v>7288168</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133856881</v>
+        <v>133856885</v>
       </c>
       <c r="B7" t="n">
-        <v>93249</v>
+        <v>79123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768793</v>
+        <v>768955</v>
       </c>
       <c r="R7" t="n">
-        <v>7288168</v>
+        <v>7287877</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
         <v>133856879</v>
       </c>
       <c r="B8" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>133856883</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133856882</v>
+        <v>133856881</v>
       </c>
       <c r="B2" t="n">
-        <v>91988</v>
+        <v>93263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768872</v>
+        <v>768793</v>
       </c>
       <c r="R2" t="n">
-        <v>7288076</v>
+        <v>7288168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133856884</v>
+        <v>133856879</v>
       </c>
       <c r="B3" t="n">
-        <v>80481</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768848</v>
+        <v>768664</v>
       </c>
       <c r="R3" t="n">
-        <v>7288092</v>
+        <v>7288089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133856880</v>
+        <v>133856882</v>
       </c>
       <c r="B4" t="n">
-        <v>98059</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768723</v>
+        <v>768872</v>
       </c>
       <c r="R4" t="n">
-        <v>7288131</v>
+        <v>7288076</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133856878</v>
+        <v>133856883</v>
       </c>
       <c r="B5" t="n">
-        <v>80486</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768814</v>
+        <v>768858</v>
       </c>
       <c r="R5" t="n">
-        <v>7288070</v>
+        <v>7288036</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133856881</v>
+        <v>133856885</v>
       </c>
       <c r="B6" t="n">
-        <v>93256</v>
+        <v>79130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768793</v>
+        <v>768955</v>
       </c>
       <c r="R6" t="n">
-        <v>7288168</v>
+        <v>7287877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133856885</v>
+        <v>133856884</v>
       </c>
       <c r="B7" t="n">
-        <v>79123</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768955</v>
+        <v>768848</v>
       </c>
       <c r="R7" t="n">
-        <v>7287877</v>
+        <v>7288092</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133856879</v>
+        <v>133856878</v>
       </c>
       <c r="B8" t="n">
-        <v>93264</v>
+        <v>80493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768664</v>
+        <v>768814</v>
       </c>
       <c r="R8" t="n">
-        <v>7288089</v>
+        <v>7288070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1417,32 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133856883</v>
+        <v>133856880</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>98066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768858</v>
+        <v>768723</v>
       </c>
       <c r="R9" t="n">
-        <v>7288036</v>
+        <v>7288131</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133856881</v>
+        <v>135266963</v>
       </c>
       <c r="B2" t="n">
-        <v>93263</v>
+        <v>92153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768793</v>
+        <v>768896</v>
       </c>
       <c r="R2" t="n">
-        <v>7288168</v>
+        <v>7287860</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133856879</v>
+        <v>135266966</v>
       </c>
       <c r="B3" t="n">
-        <v>93271</v>
+        <v>90997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,41 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768664</v>
+        <v>768844</v>
       </c>
       <c r="R3" t="n">
-        <v>7288089</v>
+        <v>7287953</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,17 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133856882</v>
+        <v>133856881</v>
       </c>
       <c r="B4" t="n">
-        <v>91995</v>
+        <v>93263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768872</v>
+        <v>768793</v>
       </c>
       <c r="R4" t="n">
-        <v>7288076</v>
+        <v>7288168</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133856883</v>
+        <v>133856879</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768858</v>
+        <v>768664</v>
       </c>
       <c r="R5" t="n">
-        <v>7288036</v>
+        <v>7288089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133856885</v>
+        <v>135266964</v>
       </c>
       <c r="B6" t="n">
-        <v>79130</v>
+        <v>93271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,41 +1112,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768955</v>
+        <v>768854</v>
       </c>
       <c r="R6" t="n">
-        <v>7287877</v>
+        <v>7287928</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,17 +1166,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,22 +1196,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133856884</v>
+        <v>133856882</v>
       </c>
       <c r="B7" t="n">
-        <v>80488</v>
+        <v>91995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768848</v>
+        <v>768872</v>
       </c>
       <c r="R7" t="n">
-        <v>7288092</v>
+        <v>7288076</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133856878</v>
+        <v>133856883</v>
       </c>
       <c r="B8" t="n">
-        <v>80493</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768814</v>
+        <v>768858</v>
       </c>
       <c r="R8" t="n">
-        <v>7288070</v>
+        <v>7288036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,12 +1383,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1417,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133856880</v>
+        <v>135266965</v>
       </c>
       <c r="B9" t="n">
-        <v>98066</v>
+        <v>79397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,41 +1431,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768723</v>
+        <v>768844</v>
       </c>
       <c r="R9" t="n">
-        <v>7288131</v>
+        <v>7287936</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,17 +1485,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,15 +1515,658 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133856885</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Arvidsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>768955</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7287877</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135266961</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>769019</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7287818</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På brandljud, koladstubbe</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135266962</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>768998</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7287845</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133856884</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Arvidsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>768848</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7288092</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133856878</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Arvidsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>768814</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7288070</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133856880</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Arvidsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>768723</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7288131</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266963</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266966</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856881</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856879</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266964</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856882</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856883</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266965</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856885</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266961</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266962</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856884</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2061,6 +2126,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856878</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2167,8 +2237,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856880</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135266963</v>
       </c>
       <c r="B2" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135266966</v>
       </c>
       <c r="B3" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135266964</v>
       </c>
       <c r="B6" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>135266965</v>
       </c>
       <c r="B9" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>135266961</v>
       </c>
       <c r="B11" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135266962</v>
       </c>
       <c r="B12" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135266963</v>
       </c>
       <c r="B2" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135266966</v>
       </c>
       <c r="B3" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135266964</v>
       </c>
       <c r="B6" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>135266965</v>
       </c>
       <c r="B9" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>135266961</v>
       </c>
       <c r="B11" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135266962</v>
       </c>
       <c r="B12" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133856881</v>
+        <v>135266963</v>
       </c>
       <c r="B2" t="n">
-        <v>93263</v>
+        <v>92227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768793</v>
+        <v>768896</v>
       </c>
       <c r="R2" t="n">
-        <v>7288168</v>
+        <v>7287860</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133856881</t>
+          <t>https://artportalen.se/Sighting/135266963</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133856879</v>
+        <v>135266966</v>
       </c>
       <c r="B3" t="n">
-        <v>93271</v>
+        <v>91069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,41 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768664</v>
+        <v>768844</v>
       </c>
       <c r="R3" t="n">
-        <v>7288089</v>
+        <v>7287953</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,27 +887,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133856879</t>
+          <t>https://artportalen.se/Sighting/135266966</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133856882</v>
+        <v>133856881</v>
       </c>
       <c r="B4" t="n">
-        <v>91995</v>
+        <v>93263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768872</v>
+        <v>768793</v>
       </c>
       <c r="R4" t="n">
-        <v>7288076</v>
+        <v>7288168</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,38 +1009,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133856882</t>
+          <t>https://artportalen.se/Sighting/133856881</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133856883</v>
+        <v>133856879</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768858</v>
+        <v>768664</v>
       </c>
       <c r="R5" t="n">
-        <v>7288036</v>
+        <v>7288089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,16 +1120,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133856883</t>
+          <t>https://artportalen.se/Sighting/133856879</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133856885</v>
+        <v>135266964</v>
       </c>
       <c r="B6" t="n">
-        <v>79130</v>
+        <v>93345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,41 +1137,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768955</v>
+        <v>768854</v>
       </c>
       <c r="R6" t="n">
-        <v>7287877</v>
+        <v>7287928</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,17 +1191,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,27 +1221,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133856885</t>
+          <t>https://artportalen.se/Sighting/135266964</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133856884</v>
+        <v>133856882</v>
       </c>
       <c r="B7" t="n">
-        <v>80488</v>
+        <v>91995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1249,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768848</v>
+        <v>768872</v>
       </c>
       <c r="R7" t="n">
-        <v>7288092</v>
+        <v>7288076</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,38 +1343,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133856884</t>
+          <t>https://artportalen.se/Sighting/133856882</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133856878</v>
+        <v>133856883</v>
       </c>
       <c r="B8" t="n">
-        <v>80493</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768814</v>
+        <v>768858</v>
       </c>
       <c r="R8" t="n">
-        <v>7288070</v>
+        <v>7288036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,12 +1418,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1451,16 +1454,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133856878</t>
+          <t>https://artportalen.se/Sighting/133856883</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133856880</v>
+        <v>135266965</v>
       </c>
       <c r="B9" t="n">
-        <v>98066</v>
+        <v>79465</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,41 +1471,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768723</v>
+        <v>768844</v>
       </c>
       <c r="R9" t="n">
-        <v>7288131</v>
+        <v>7287936</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,17 +1525,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,16 +1555,689 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266965</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133856885</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Arvidsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>768955</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7287877</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856885</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135266961</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>769019</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7287818</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På brandljud, koladstubbe</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266961</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135266962</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sör klöverberget  A 25676-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>768998</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7287845</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266962</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133856884</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Arvidsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>768848</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7288092</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856884</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133856878</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Arvidsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>768814</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7288070</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856878</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133856880</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Arvidsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>768723</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7288131</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133856880</t>
         </is>
@@ -1576,6 +2253,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25676-2026 artfynd.xlsx
+++ b/artfynd/A 25676-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135266963</v>
       </c>
       <c r="B2" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135266966</v>
       </c>
       <c r="B3" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135266964</v>
       </c>
       <c r="B6" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
